--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_laag.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_laag.xlsx
@@ -406,7 +406,7 @@
         <v>811</v>
       </c>
       <c r="C2">
-        <v>520</v>
+        <v>606</v>
       </c>
       <c r="D2">
         <v>378</v>
@@ -418,7 +418,7 @@
         <v>816</v>
       </c>
       <c r="G2">
-        <v>706</v>
+        <v>735</v>
       </c>
       <c r="H2">
         <v>894</v>
@@ -432,7 +432,7 @@
         <v>854</v>
       </c>
       <c r="C3">
-        <v>542</v>
+        <v>643</v>
       </c>
       <c r="D3">
         <v>354</v>
@@ -444,7 +444,7 @@
         <v>858</v>
       </c>
       <c r="G3">
-        <v>713</v>
+        <v>766</v>
       </c>
       <c r="H3">
         <v>921</v>
@@ -458,7 +458,7 @@
         <v>735</v>
       </c>
       <c r="C4">
-        <v>564</v>
+        <v>583</v>
       </c>
       <c r="D4">
         <v>200</v>
@@ -470,7 +470,7 @@
         <v>742</v>
       </c>
       <c r="G4">
-        <v>637</v>
+        <v>650</v>
       </c>
       <c r="H4">
         <v>852</v>
@@ -484,7 +484,7 @@
         <v>916</v>
       </c>
       <c r="C5">
-        <v>663</v>
+        <v>727</v>
       </c>
       <c r="D5">
         <v>130</v>
@@ -496,7 +496,7 @@
         <v>917</v>
       </c>
       <c r="G5">
-        <v>714</v>
+        <v>770</v>
       </c>
       <c r="H5">
         <v>966</v>
@@ -510,7 +510,7 @@
         <v>900</v>
       </c>
       <c r="C6">
-        <v>648</v>
+        <v>710</v>
       </c>
       <c r="D6">
         <v>66</v>
@@ -522,7 +522,7 @@
         <v>902</v>
       </c>
       <c r="G6">
-        <v>672</v>
+        <v>733</v>
       </c>
       <c r="H6">
         <v>957</v>
@@ -536,7 +536,7 @@
         <v>939</v>
       </c>
       <c r="C7">
-        <v>714</v>
+        <v>751</v>
       </c>
       <c r="D7">
         <v>111</v>
@@ -548,7 +548,7 @@
         <v>940</v>
       </c>
       <c r="G7">
-        <v>751</v>
+        <v>787</v>
       </c>
       <c r="H7">
         <v>979</v>
@@ -562,7 +562,7 @@
         <v>833</v>
       </c>
       <c r="C8">
-        <v>286</v>
+        <v>465</v>
       </c>
       <c r="D8">
         <v>109</v>
@@ -574,7 +574,7 @@
         <v>833</v>
       </c>
       <c r="G8">
-        <v>357</v>
+        <v>512</v>
       </c>
       <c r="H8">
         <v>858</v>
@@ -588,7 +588,7 @@
         <v>946</v>
       </c>
       <c r="C9">
-        <v>607</v>
+        <v>749</v>
       </c>
       <c r="D9">
         <v>176</v>
@@ -600,7 +600,7 @@
         <v>947</v>
       </c>
       <c r="G9">
-        <v>666</v>
+        <v>807</v>
       </c>
       <c r="H9">
         <v>969</v>
@@ -614,7 +614,7 @@
         <v>961</v>
       </c>
       <c r="C10">
-        <v>683</v>
+        <v>754</v>
       </c>
       <c r="D10">
         <v>266</v>
@@ -626,7 +626,7 @@
         <v>962</v>
       </c>
       <c r="G10">
-        <v>797</v>
+        <v>840</v>
       </c>
       <c r="H10">
         <v>985</v>
@@ -640,7 +640,7 @@
         <v>953</v>
       </c>
       <c r="C11">
-        <v>687</v>
+        <v>756</v>
       </c>
       <c r="D11">
         <v>232</v>
@@ -652,7 +652,7 @@
         <v>954</v>
       </c>
       <c r="G11">
-        <v>788</v>
+        <v>830</v>
       </c>
       <c r="H11">
         <v>985</v>
@@ -666,7 +666,7 @@
         <v>875</v>
       </c>
       <c r="C12">
-        <v>701</v>
+        <v>821</v>
       </c>
       <c r="D12">
         <v>56</v>
@@ -678,7 +678,7 @@
         <v>878</v>
       </c>
       <c r="G12">
-        <v>721</v>
+        <v>841</v>
       </c>
       <c r="H12">
         <v>963</v>
@@ -692,7 +692,7 @@
         <v>957</v>
       </c>
       <c r="C13">
-        <v>682</v>
+        <v>750</v>
       </c>
       <c r="D13">
         <v>203</v>
@@ -704,7 +704,7 @@
         <v>958</v>
       </c>
       <c r="G13">
-        <v>774</v>
+        <v>817</v>
       </c>
       <c r="H13">
         <v>983</v>
